--- a/templates/FUNCEF IMOB - template.xlsx
+++ b/templates/FUNCEF IMOB - template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20370" yWindow="-60" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$G$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$G$43</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -1229,7 +1229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="56" min="1" max="1"/>
@@ -1237,8 +1237,8 @@
     <col width="5.42578125" customWidth="1" style="56" min="8" max="8"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="56" min="9" max="9"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="56" min="10" max="10"/>
-    <col width="9.140625" customWidth="1" style="56" min="11" max="18"/>
-    <col width="9.140625" customWidth="1" style="56" min="19" max="16384"/>
+    <col width="9.140625" customWidth="1" style="56" min="11" max="19"/>
+    <col width="9.140625" customWidth="1" style="56" min="20" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1398,111 +1398,111 @@
     <row r="17" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B17" s="28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="29" t="n">
-        <v>13.4738776</v>
+        <v>13.5914432</v>
       </c>
       <c r="D17" s="30" t="n">
-        <v>0.0002381544584699746</v>
+        <v>0.0002336648038316902</v>
       </c>
       <c r="E17" s="30" t="n">
-        <v>0.0005475854278347292</v>
+        <v>0.0004859476104168703</v>
       </c>
       <c r="F17" s="31" t="n">
-        <v>0.4349174509842029</v>
+        <v>0.4808436111687858</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>-0.0009170533056662711</v>
+        <v>0.004910425210446823</v>
       </c>
     </row>
     <row r="18" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B18" s="32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="33" t="n">
-        <v>13.4706695</v>
+        <v>13.5882681</v>
       </c>
       <c r="D18" s="34" t="n">
-        <v>0.000648933523190065</v>
+        <v>0.0002974552678645104</v>
       </c>
       <c r="E18" s="34" t="n">
-        <v>0.0005475854278347292</v>
+        <v>0.0004859476104168703</v>
       </c>
       <c r="F18" s="35" t="n">
-        <v>1.185081797658656</v>
+        <v>0.6121138606059577</v>
       </c>
       <c r="G18" s="34" t="n">
-        <v>0.0009698038351333427</v>
+        <v>0.0002801602825248661</v>
       </c>
     </row>
     <row r="19" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="33" t="n">
-        <v>13.4619336</v>
+        <v>13.5842274</v>
       </c>
       <c r="D19" s="34" t="n">
-        <v>-0.001315559214597473</v>
+        <v>0.002671864687268322</v>
       </c>
       <c r="E19" s="34" t="n">
-        <v>0.0005475854278347292</v>
+        <v>0.0004859476104168703</v>
       </c>
       <c r="F19" s="35" t="n">
-        <v>-2.402473016492563</v>
+        <v>5.498256663874243</v>
       </c>
       <c r="G19" s="34" t="n">
-        <v>-0.001486203423446297</v>
+        <v>0.002675085368210928</v>
       </c>
     </row>
     <row r="20" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B20" s="32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="33" t="n">
-        <v>13.4796669</v>
+        <v>13.5480289</v>
       </c>
       <c r="D20" s="34" t="n">
-        <v>-0.001831454987454517</v>
+        <v>-0.0006963025325743555</v>
       </c>
       <c r="E20" s="34" t="n">
-        <v>0.0005475854278347292</v>
+        <v>0.0004859476104168703</v>
       </c>
       <c r="F20" s="35" t="n">
-        <v>-3.344601397989141</v>
+        <v>-1.432875720856065</v>
       </c>
       <c r="G20" s="34" t="n">
-        <v>9.063037308632005e-05</v>
+        <v>-0.001710874990352274</v>
       </c>
     </row>
     <row r="21" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="33" t="n">
-        <v>13.5043996</v>
+        <v>13.557469</v>
       </c>
       <c r="D21" s="34" t="n">
-        <v>0.0005562836450154762</v>
+        <v>-0.001444073894176667</v>
       </c>
       <c r="E21" s="34" t="n">
-        <v>0.0005475854278347292</v>
+        <v>0.0004859476104168703</v>
       </c>
       <c r="F21" s="35" t="n">
-        <v>1.015884676141112</v>
+        <v>-2.971665799401438</v>
       </c>
       <c r="G21" s="34" t="n">
-        <v>-0.0005719387689082644</v>
+        <v>0.000347441160196027</v>
       </c>
     </row>
     <row r="22" ht="15.95" customHeight="1">
@@ -1548,21 +1548,21 @@
     <row r="24" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="B24" s="36" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="37" t="inlineStr"/>
       <c r="D24" s="30" t="n">
-        <v>-0.002739390387421659</v>
+        <v>0.00380109968286213</v>
       </c>
       <c r="E24" s="30" t="n">
-        <v>0.01045555689724331</v>
+        <v>0.003406596337946821</v>
       </c>
       <c r="F24" s="31" t="n">
-        <v>-0.262003297800801</v>
+        <v>1.115805720954036</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>-0.01414625293009431</v>
+        <v>0.01040156876119025</v>
       </c>
       <c r="H24" s="38" t="n"/>
     </row>
@@ -1574,16 +1574,16 @@
       </c>
       <c r="C25" s="41" t="inlineStr"/>
       <c r="D25" s="34" t="n">
-        <v>0.002225594774300399</v>
+        <v>-0.0006717287501382119</v>
       </c>
       <c r="E25" s="34" t="n">
-        <v>0.01170605089235655</v>
+        <v>0.01333731957224682</v>
       </c>
       <c r="F25" s="35" t="n">
-        <v>0.1901234493823702</v>
+        <v>-0.05036459886107773</v>
       </c>
       <c r="G25" s="34" t="n">
-        <v>-0.005238640584375398</v>
+        <v>0.009613820770912662</v>
       </c>
       <c r="H25" s="38" t="n"/>
     </row>
@@ -1595,16 +1595,16 @@
       </c>
       <c r="C26" s="41" t="inlineStr"/>
       <c r="D26" s="34" t="n">
-        <v>0.05277492042018972</v>
+        <v>0.045368393353169</v>
       </c>
       <c r="E26" s="34" t="n">
-        <v>0.03360603827432063</v>
+        <v>0.03779464677180777</v>
       </c>
       <c r="F26" s="35" t="n">
-        <v>1.570399937933672</v>
+        <v>1.200392045653691</v>
       </c>
       <c r="G26" s="34" t="n">
-        <v>0.02702954609003627</v>
+        <v>0.03391362969425371</v>
       </c>
       <c r="H26" s="38" t="n"/>
     </row>
@@ -1616,16 +1616,16 @@
       </c>
       <c r="C27" s="41" t="inlineStr"/>
       <c r="D27" s="34" t="n">
-        <v>0.1362587587443449</v>
+        <v>0.1280518634292864</v>
       </c>
       <c r="E27" s="34" t="n">
-        <v>0.05895060576320454</v>
+        <v>0.06366721567790345</v>
       </c>
       <c r="F27" s="35" t="n">
-        <v>2.311405573874427</v>
+        <v>2.011268469428741</v>
       </c>
       <c r="G27" s="34" t="n">
-        <v>0.08199135899450116</v>
+        <v>0.09321067373329073</v>
       </c>
       <c r="H27" s="38" t="n"/>
     </row>
@@ -1638,60 +1638,60 @@
       </c>
       <c r="C28" s="41" t="inlineStr"/>
       <c r="D28" s="34" t="n">
-        <v>0.2701416684619027</v>
+        <v>0.2720035422145362</v>
       </c>
       <c r="E28" s="34" t="n">
-        <v>0.1151138062074684</v>
+        <v>0.1188945754261794</v>
       </c>
       <c r="F28" s="35" t="n">
-        <v>2.346735612017114</v>
+        <v>2.287770835965689</v>
       </c>
       <c r="G28" s="34" t="n">
-        <v>0.2701416684619027</v>
+        <v>0.2720035422145362</v>
       </c>
       <c r="H28" s="38" t="n"/>
     </row>
-    <row r="29" ht="15.95" customFormat="1" customHeight="1" s="19">
+    <row r="29" ht="15.95" customFormat="1" customHeight="1" s="39">
       <c r="A29" s="32" t="n"/>
       <c r="B29" s="40" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr"/>
       <c r="D29" s="34" t="n">
-        <v>0.03941609001718249</v>
+        <v>0.2771013137825342</v>
       </c>
       <c r="E29" s="34" t="n">
-        <v>0.03131846775379654</v>
+        <v>0.2678273283757466</v>
       </c>
       <c r="F29" s="35" t="n">
-        <v>1.258557421360575</v>
+        <v>1.034626733063538</v>
       </c>
       <c r="G29" s="34" t="n">
-        <v>0.0215452505886935</v>
-      </c>
-      <c r="H29" s="54" t="n"/>
+        <v>0.2771013137825342</v>
+      </c>
+      <c r="H29" s="38" t="n"/>
     </row>
     <row r="30" ht="15.95" customFormat="1" customHeight="1" s="19">
       <c r="A30" s="32" t="n"/>
       <c r="B30" s="40" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="41" t="inlineStr"/>
       <c r="D30" s="34" t="n">
-        <v>0.2772849041968553</v>
+        <v>0.04848545964486295</v>
       </c>
       <c r="E30" s="34" t="n">
-        <v>0.1196837808443612</v>
+        <v>0.04009657034346281</v>
       </c>
       <c r="F30" s="35" t="n">
-        <v>2.316812706288426</v>
+        <v>1.20921712828658</v>
       </c>
       <c r="G30" s="34" t="n">
-        <v>0.2114797129911303</v>
+        <v>0.03589638996532729</v>
       </c>
       <c r="H30" s="54" t="n"/>
     </row>
@@ -1699,21 +1699,21 @@
       <c r="A31" s="32" t="n"/>
       <c r="B31" s="40" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr"/>
       <c r="D31" s="34" t="n">
-        <v>-0.01630062723239178</v>
+        <v>0.2772849041968553</v>
       </c>
       <c r="E31" s="34" t="n">
-        <v>0.1269692278301353</v>
-      </c>
-      <c r="F31" s="34" t="n">
-        <v>-0.128382502681669</v>
+        <v>0.1196837808443612</v>
+      </c>
+      <c r="F31" s="35" t="n">
+        <v>2.316812706288426</v>
       </c>
       <c r="G31" s="34" t="n">
-        <v>-0.05893224377383777</v>
+        <v>0.2114797129911303</v>
       </c>
       <c r="H31" s="54" t="n"/>
     </row>
@@ -1721,185 +1721,207 @@
       <c r="A32" s="32" t="n"/>
       <c r="B32" s="40" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="41" t="inlineStr"/>
       <c r="D32" s="34" t="n">
-        <v>0.3473877599999999</v>
+        <v>-0.01630062723239178</v>
       </c>
       <c r="E32" s="34" t="n">
-        <v>0.3163717226262865</v>
+        <v>0.1269692278301353</v>
       </c>
       <c r="F32" s="34" t="n">
-        <v>1.098036692774692</v>
+        <v>-0.128382502681669</v>
       </c>
       <c r="G32" s="34" t="n">
-        <v>0.2189159292035399</v>
+        <v>-0.05893224377383777</v>
       </c>
       <c r="H32" s="54" t="n"/>
     </row>
-    <row r="33" ht="15.95" customHeight="1">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="25" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
-      <c r="B34" s="55" t="inlineStr">
+    <row r="33" ht="15.95" customFormat="1" customHeight="1" s="19">
+      <c r="A33" s="32" t="n"/>
+      <c r="B33" s="40" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr"/>
+      <c r="D33" s="34" t="n">
+        <v>0.35914432</v>
+      </c>
+      <c r="E33" s="34" t="n">
+        <v>0.3275760657934523</v>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>1.09636923299046</v>
+      </c>
+      <c r="G33" s="34" t="n">
+        <v>0.2360398230088496</v>
+      </c>
+      <c r="H33" s="54" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="B35" s="55" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="B35" s="42" t="inlineStr">
+      <c r="H35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="15.95" customHeight="1">
+      <c r="B36" s="42" t="inlineStr">
         <is>
           <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="23" t="n">
-        <v>529489249.04</v>
-      </c>
-      <c r="F35" s="23" t="n"/>
-      <c r="G35" s="23" t="n"/>
-      <c r="H35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customHeight="1">
-      <c r="B36" s="43" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
         </is>
       </c>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="19" t="n"/>
       <c r="E36" s="23" t="n">
-        <v>471697853.6830952</v>
+        <v>534109277.7</v>
       </c>
       <c r="F36" s="23" t="n"/>
       <c r="G36" s="23" t="n"/>
       <c r="H36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
-      <c r="B37" s="42" t="n"/>
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
+      <c r="E37" s="23" t="n">
+        <v>476208410.6205159</v>
+      </c>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="23" t="n"/>
       <c r="H37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="44" t="inlineStr">
-        <is>
-          <t>¹Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C38" s="45" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="n"/>
-      <c r="E38" s="20" t="n"/>
-      <c r="F38" s="20" t="n"/>
-      <c r="G38" s="20" t="n"/>
+      <c r="B38" s="42" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="19" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="19" t="n"/>
       <c r="H38" s="4" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
       <c r="A39" s="4" t="n"/>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">² Cota Inicial em: </t>
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>¹Data de Referência:</t>
         </is>
       </c>
       <c r="C39" s="45" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="D39" s="21" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="21" t="n"/>
-      <c r="G39" s="21" t="n"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="20" t="n"/>
       <c r="H39" s="4" t="n"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
       <c r="A40" s="4" t="n"/>
-      <c r="B40" s="14" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">² Cota Inicial em: </t>
+        </is>
+      </c>
+      <c r="C40" s="45" t="inlineStr">
+        <is>
+          <t>2023-11-29</t>
+        </is>
+      </c>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
       <c r="H40" s="4" t="n"/>
     </row>
-    <row r="41" ht="40.5" customHeight="1">
+    <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="4" t="n"/>
-      <c r="B41" s="26" t="inlineStr">
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="40.5" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="C41" s="26" t="n"/>
-      <c r="D41" s="26" t="n"/>
-      <c r="E41" s="26" t="n"/>
-      <c r="F41" s="26" t="n"/>
-      <c r="G41" s="26" t="n"/>
-      <c r="H41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="27" t="n"/>
-      <c r="D42" s="27" t="n"/>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="27" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="26" t="n"/>
+      <c r="F42" s="26" t="n"/>
+      <c r="G42" s="26" t="n"/>
       <c r="H42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-      <c r="G43" s="16" t="n"/>
+      <c r="B43" s="27" t="n"/>
+      <c r="C43" s="27" t="n"/>
+      <c r="D43" s="27" t="n"/>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="n"/>
       <c r="H43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="12" t="n"/>
-      <c r="G44" s="12" t="n"/>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="16" t="n"/>
       <c r="H44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="17" t="n"/>
       <c r="C45" s="18" t="n"/>
       <c r="D45" s="12" t="n"/>
       <c r="E45" s="12" t="n"/>
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="12" t="n"/>
+      <c r="H45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="18" t="n"/>
+      <c r="D46" s="12" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="12" t="n"/>
+      <c r="G46" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="88" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="86"/>
 </worksheet>
 </file>